--- a/Pruebas calificadas/COLEGIO GRABRIEL GARCIA MARQUEZ (IED)-701_CALIFICADO.xlsx
+++ b/Pruebas calificadas/COLEGIO GRABRIEL GARCIA MARQUEZ (IED)-701_CALIFICADO.xlsx
@@ -807,11 +807,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A2" s="2" t="inlineStr"/>
       <c r="B2" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -1060,11 +1056,7 @@
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A3" s="2" t="inlineStr"/>
       <c r="B3" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -1313,11 +1305,7 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A4" s="2" t="inlineStr"/>
       <c r="B4" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -1566,11 +1554,7 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A5" s="2" t="inlineStr"/>
       <c r="B5" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -1819,11 +1803,7 @@
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A6" s="2" t="inlineStr"/>
       <c r="B6" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -2072,11 +2052,7 @@
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A7" s="2" t="inlineStr"/>
       <c r="B7" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -2325,11 +2301,7 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A8" s="2" t="inlineStr"/>
       <c r="B8" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -2578,11 +2550,7 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A9" s="2" t="inlineStr"/>
       <c r="B9" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -2831,11 +2799,7 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A10" s="2" t="inlineStr"/>
       <c r="B10" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -3084,11 +3048,7 @@
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A11" s="2" t="inlineStr"/>
       <c r="B11" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -3333,11 +3293,7 @@
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A12" s="2" t="inlineStr"/>
       <c r="B12" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -3586,11 +3542,7 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A13" s="2" t="inlineStr"/>
       <c r="B13" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -3839,11 +3791,7 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A14" s="2" t="inlineStr"/>
       <c r="B14" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -4092,11 +4040,7 @@
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A15" s="2" t="inlineStr"/>
       <c r="B15" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -4345,11 +4289,7 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A16" s="2" t="inlineStr"/>
       <c r="B16" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -4598,11 +4538,7 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A17" s="2" t="inlineStr"/>
       <c r="B17" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -4851,11 +4787,7 @@
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A18" s="2" t="inlineStr"/>
       <c r="B18" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -5104,11 +5036,7 @@
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A19" s="2" t="inlineStr"/>
       <c r="B19" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -5357,11 +5285,7 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A20" s="2" t="inlineStr"/>
       <c r="B20" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -5610,11 +5534,7 @@
       </c>
     </row>
     <row r="21">
-      <c r="A21" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A21" s="2" t="inlineStr"/>
       <c r="B21" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -5863,11 +5783,7 @@
       </c>
     </row>
     <row r="22">
-      <c r="A22" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A22" s="2" t="inlineStr"/>
       <c r="B22" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -6116,11 +6032,7 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A23" s="2" t="inlineStr"/>
       <c r="B23" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -6337,11 +6249,7 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A24" s="2" t="inlineStr"/>
       <c r="B24" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -6590,11 +6498,7 @@
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A25" s="2" t="inlineStr"/>
       <c r="B25" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -6843,11 +6747,7 @@
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A26" s="2" t="inlineStr"/>
       <c r="B26" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -7096,11 +6996,7 @@
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A27" s="2" t="inlineStr"/>
       <c r="B27" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -7349,11 +7245,7 @@
       </c>
     </row>
     <row r="28">
-      <c r="A28" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A28" s="2" t="inlineStr"/>
       <c r="B28" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -7602,11 +7494,7 @@
       </c>
     </row>
     <row r="29">
-      <c r="A29" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A29" s="2" t="inlineStr"/>
       <c r="B29" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -7847,11 +7735,7 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A30" s="2" t="inlineStr"/>
       <c r="B30" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -8100,11 +7984,7 @@
       </c>
     </row>
     <row r="31">
-      <c r="A31" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A31" s="2" t="inlineStr"/>
       <c r="B31" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -8353,11 +8233,7 @@
       </c>
     </row>
     <row r="32">
-      <c r="A32" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A32" s="2" t="inlineStr"/>
       <c r="B32" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -8606,11 +8482,7 @@
       </c>
     </row>
     <row r="33">
-      <c r="A33" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A33" s="2" t="inlineStr"/>
       <c r="B33" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -8859,11 +8731,7 @@
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A34" s="2" t="inlineStr"/>
       <c r="B34" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -9112,11 +8980,7 @@
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A35" s="2" t="inlineStr"/>
       <c r="B35" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -9365,11 +9229,7 @@
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A36" s="2" t="inlineStr"/>
       <c r="B36" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -9618,11 +9478,7 @@
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A37" s="2" t="inlineStr"/>
       <c r="B37" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -9871,11 +9727,7 @@
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A38" s="2" t="inlineStr"/>
       <c r="B38" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -10124,11 +9976,7 @@
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A39" s="2" t="inlineStr"/>
       <c r="B39" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -10377,11 +10225,7 @@
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A40" s="2" t="inlineStr"/>
       <c r="B40" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -10630,11 +10474,7 @@
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A41" s="2" t="inlineStr"/>
       <c r="B41" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -10883,11 +10723,7 @@
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A42" s="2" t="inlineStr"/>
       <c r="B42" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -11088,11 +10924,7 @@
       </c>
     </row>
     <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A43" s="2" t="inlineStr"/>
       <c r="B43" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -11297,11 +11129,7 @@
       </c>
     </row>
     <row r="44">
-      <c r="A44" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A44" s="2" t="inlineStr"/>
       <c r="B44" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -11542,11 +11370,7 @@
       </c>
     </row>
     <row r="45">
-      <c r="A45" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A45" s="2" t="inlineStr"/>
       <c r="B45" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -11795,11 +11619,7 @@
       </c>
     </row>
     <row r="46">
-      <c r="A46" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A46" s="2" t="inlineStr"/>
       <c r="B46" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -12048,11 +11868,7 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A47" s="2" t="inlineStr"/>
       <c r="B47" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -12297,11 +12113,7 @@
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A48" s="2" t="inlineStr"/>
       <c r="B48" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -12550,11 +12362,7 @@
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A49" s="2" t="inlineStr"/>
       <c r="B49" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -12803,11 +12611,7 @@
       </c>
     </row>
     <row r="50">
-      <c r="A50" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A50" s="2" t="inlineStr"/>
       <c r="B50" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -13056,11 +12860,7 @@
       </c>
     </row>
     <row r="51">
-      <c r="A51" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A51" s="2" t="inlineStr"/>
       <c r="B51" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -13309,11 +13109,7 @@
       </c>
     </row>
     <row r="52">
-      <c r="A52" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A52" s="2" t="inlineStr"/>
       <c r="B52" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -13562,11 +13358,7 @@
       </c>
     </row>
     <row r="53">
-      <c r="A53" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A53" s="2" t="inlineStr"/>
       <c r="B53" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -13815,11 +13607,7 @@
       </c>
     </row>
     <row r="54">
-      <c r="A54" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A54" s="2" t="inlineStr"/>
       <c r="B54" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -14068,11 +13856,7 @@
       </c>
     </row>
     <row r="55">
-      <c r="A55" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A55" s="2" t="inlineStr"/>
       <c r="B55" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -14321,11 +14105,7 @@
       </c>
     </row>
     <row r="56">
-      <c r="A56" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A56" s="2" t="inlineStr"/>
       <c r="B56" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -14574,11 +14354,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A57" s="2" t="inlineStr"/>
       <c r="B57" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -14827,11 +14603,7 @@
       </c>
     </row>
     <row r="58">
-      <c r="A58" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A58" s="2" t="inlineStr"/>
       <c r="B58" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
@@ -15080,11 +14852,7 @@
       </c>
     </row>
     <row r="59">
-      <c r="A59" s="2" t="inlineStr">
-        <is>
-          <t>CONTROL</t>
-        </is>
-      </c>
+      <c r="A59" s="2" t="inlineStr"/>
       <c r="B59" s="2" t="inlineStr">
         <is>
           <t>211001032501</t>
